--- a/education_surveys/007_pedagogical_research_awareness_survey--education_surveys.xlsx
+++ b/education_surveys/007_pedagogical_research_awareness_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>welcome</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Welcome</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This survey aims to understand your level of awareness about pedagogical research.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,20 +552,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>research_interest</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Awareness Level</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>What is your current level of awareness about pedagogical research?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>teaching_initiatives</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Research Project</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide a brief description of a recent pedagogical research project you've participated in.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,30 +596,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>first_page_note</t>
+          <t>page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>first_page_note</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Theories Understanding</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>What is your current level of understanding of pedagogical theories?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,20 +633,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>teaching_principles</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Collaboration Level</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>What is your level of collaboration with other researchers in pedagogical research?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +660,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>page_6</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Resource Access</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How do you usually access pedagogical research resources?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,20 +687,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>page_7</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Favorite Resource</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>What is your favorite pedagogical research resource?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,112 +714,132 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>page_8</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Resource Evaluation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>How do you usually evaluate the quality of pedagogical research?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>first_page_date</t>
+          <t>page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>first_page_date</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Teaching Practice</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Can you provide an example of how you've applied pedagogical research in your teaching practice?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>first_page_time</t>
+          <t>page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>first_page_time</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Support Level</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>What is your current level of support from your institution for pedagogical research?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>first_page_email</t>
+          <t>page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>first_page_email</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Challenges</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>What do you think are the main challenges in pedagogical research?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>first_page_phone</t>
+          <t>page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>first_page_phone</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>What is the expected outcome of this survey?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,10 +849,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>page_13</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Teaching Initiative</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Can you provide a brief description of a pedagogical research initiative you'd like to propose or support?</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,7 +866,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,20 +876,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>page_14</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Research Frequency</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>How frequently do you conduct pedagogical research?</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -847,241 +903,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>page_15</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Conclusion</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Thank you for participating in this survey!</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>first_page_note</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>first_page_note</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>page_17</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>page_18</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>first_page_date</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>first_page_date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>page_20</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>page_21</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>page_22</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>first_page_time</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>first_page_time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>page_24</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>first_page_phone</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>first_page_phone</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +928,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +961,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +978,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,522 +995,471 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>page_4_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>page_4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_3_choices</t>
+          <t>page_4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_13_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>page_14_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>page_15_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>page_15_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>page_15_choices</t>
+          <t>page_7_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>page_17_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>page_17_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>page_17_choices</t>
+          <t>page_8_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>page_18_choices</t>
+          <t>page_10_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>page_18_choices</t>
+          <t>page_10_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>page_18_choices</t>
+          <t>page_10_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>page_20_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>page_20_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>page_20_choices</t>
+          <t>page_11_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>page_21_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>page_21_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>page_21_choices</t>
+          <t>page_12_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>page_22_choices</t>
+          <t>page_14_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>page_22_choices</t>
+          <t>page_14_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>page_22_choices</t>
+          <t>page_14_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option_3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>page_24_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>page_24_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>page_24_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>option_3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
